--- a/countries/no/2026-2029.xlsx
+++ b/countries/no/2026-2029.xlsx
@@ -48568,13 +48568,13 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O334" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R334" t="n">
-        <v>0.2653463738693259</v>
+        <v>0.2476566156113709</v>
       </c>
       <c r="U334" t="inlineStr">
         <is>
@@ -51016,13 +51016,13 @@
         </is>
       </c>
       <c r="N351" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="O351" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="R351" t="n">
-        <v>2.600394463919394</v>
+        <v>2.511945672629619</v>
       </c>
       <c r="U351" t="inlineStr">
         <is>
@@ -54184,13 +54184,13 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O373" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R373" t="n">
-        <v>0.4245541981909216</v>
+        <v>0.4422439564488765</v>
       </c>
       <c r="U373" t="inlineStr">
         <is>
@@ -54616,13 +54616,13 @@
         </is>
       </c>
       <c r="N376" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O376" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R376" t="n">
-        <v>0.2122770990954608</v>
+        <v>0.2299668573534158</v>
       </c>
       <c r="U376" t="inlineStr">
         <is>
@@ -57784,13 +57784,13 @@
         </is>
       </c>
       <c r="N398" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O398" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="R398" t="n">
-        <v>2.105081232696652</v>
+        <v>2.122770990954607</v>
       </c>
       <c r="U398" t="inlineStr">
         <is>
@@ -58216,13 +58216,13 @@
         </is>
       </c>
       <c r="N401" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O401" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R401" t="n">
-        <v>1.43287041889436</v>
+        <v>1.450560177152315</v>
       </c>
       <c r="U401" t="inlineStr">
         <is>
@@ -58648,13 +58648,13 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O404" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R404" t="n">
-        <v>0.4422439564488765</v>
+        <v>0.4599337147068316</v>
       </c>
       <c r="U404" t="inlineStr">
         <is>
@@ -59080,13 +59080,13 @@
         </is>
       </c>
       <c r="N407" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O407" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R407" t="n">
-        <v>0.1061385495477304</v>
+        <v>0.1238283078056854</v>
       </c>
       <c r="U407" t="inlineStr">
         <is>
@@ -60088,13 +60088,13 @@
         </is>
       </c>
       <c r="N414" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O414" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="R414" t="n">
-        <v>5.890689499899036</v>
+        <v>5.908379258156991</v>
       </c>
       <c r="U414" t="inlineStr">
         <is>
@@ -60376,13 +60376,13 @@
         </is>
       </c>
       <c r="N416" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O416" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="R416" t="n">
-        <v>6.580590071959284</v>
+        <v>6.598279830217238</v>
       </c>
       <c r="U416" t="inlineStr">
         <is>
@@ -60808,13 +60808,13 @@
         </is>
       </c>
       <c r="N419" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O419" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R419" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.07075903303182025</v>
       </c>
       <c r="U419" t="inlineStr">
         <is>
@@ -60952,13 +60952,13 @@
         </is>
       </c>
       <c r="N420" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="O420" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="R420" t="n">
-        <v>0.1945873408375057</v>
+        <v>0.3361054069011462</v>
       </c>
       <c r="U420" t="inlineStr">
         <is>
@@ -61240,13 +61240,13 @@
         </is>
       </c>
       <c r="N422" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O422" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R422" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="U422" t="inlineStr">
         <is>
@@ -61384,13 +61384,13 @@
         </is>
       </c>
       <c r="N423" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O423" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R423" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.08844879128977531</v>
       </c>
       <c r="U423" t="inlineStr">
         <is>
@@ -61528,13 +61528,13 @@
         </is>
       </c>
       <c r="N424" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="O424" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="R424" t="n">
-        <v>0.6368312972863822</v>
+        <v>1.220593319798899</v>
       </c>
       <c r="U424" t="inlineStr">
         <is>
@@ -61960,13 +61960,13 @@
         </is>
       </c>
       <c r="N427" t="n">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="O427" t="n">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="R427" t="n">
-        <v>1.645147517989821</v>
+        <v>2.476566156113709</v>
       </c>
       <c r="U427" t="inlineStr">
         <is>
@@ -62104,13 +62104,13 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O428" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="R428" t="n">
-        <v>0.1768975825795506</v>
+        <v>0.2476566156113709</v>
       </c>
       <c r="U428" t="inlineStr">
         <is>
@@ -63112,13 +63112,13 @@
         </is>
       </c>
       <c r="N435" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O435" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R435" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="U435" t="inlineStr">
         <is>
@@ -63400,13 +63400,13 @@
         </is>
       </c>
       <c r="N437" t="n">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="O437" t="n">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="R437" t="n">
-        <v>2.458876397855754</v>
+        <v>3.644090201138743</v>
       </c>
       <c r="U437" t="inlineStr">
         <is>
@@ -63544,13 +63544,13 @@
         </is>
       </c>
       <c r="N438" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O438" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="R438" t="n">
-        <v>0.3007258903852361</v>
+        <v>0.6191415390284272</v>
       </c>
       <c r="U438" t="inlineStr">
         <is>
@@ -63688,13 +63688,13 @@
         </is>
       </c>
       <c r="N439" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O439" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R439" t="n">
-        <v>0.2476566156113709</v>
+        <v>0.3184156486431911</v>
       </c>
       <c r="U439" t="inlineStr">
         <is>
@@ -63832,13 +63832,13 @@
         </is>
       </c>
       <c r="N440" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O440" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R440" t="n">
-        <v>0.08844879128977531</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="U440" t="inlineStr">
         <is>
@@ -63976,13 +63976,13 @@
         </is>
       </c>
       <c r="N441" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O441" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R441" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.07075903303182025</v>
       </c>
       <c r="U441" t="inlineStr">
         <is>
@@ -64120,13 +64120,13 @@
         </is>
       </c>
       <c r="N442" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="O442" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="R442" t="n">
-        <v>0.5306927477386518</v>
+        <v>0.7429698468341126</v>
       </c>
       <c r="U442" t="inlineStr">
         <is>
@@ -64264,13 +64264,13 @@
         </is>
       </c>
       <c r="N443" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O443" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R443" t="n">
-        <v>0.1061385495477304</v>
+        <v>0.1415180660636405</v>
       </c>
       <c r="U443" t="inlineStr">
         <is>
@@ -64552,13 +64552,13 @@
         </is>
       </c>
       <c r="N445" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="O445" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="R445" t="n">
-        <v>0.6191415390284272</v>
+        <v>1.008316220703439</v>
       </c>
       <c r="U445" t="inlineStr">
         <is>
@@ -64984,13 +64984,13 @@
         </is>
       </c>
       <c r="N448" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="O448" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="R448" t="n">
-        <v>0.548382505996607</v>
+        <v>0.9021776711557081</v>
       </c>
       <c r="U448" t="inlineStr">
         <is>
@@ -65128,13 +65128,13 @@
         </is>
       </c>
       <c r="N449" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="O449" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="R449" t="n">
-        <v>0.2299668573534158</v>
+        <v>0.3537951651591013</v>
       </c>
       <c r="U449" t="inlineStr">
         <is>
@@ -65416,13 +65416,13 @@
         </is>
       </c>
       <c r="N451" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O451" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R451" t="n">
-        <v>0.07075903303182025</v>
+        <v>0.1768975825795506</v>
       </c>
       <c r="U451" t="inlineStr">
         <is>
@@ -65848,13 +65848,13 @@
         </is>
       </c>
       <c r="N454" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O454" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R454" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="U454" t="inlineStr">
         <is>
@@ -66136,13 +66136,13 @@
         </is>
       </c>
       <c r="N456" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O456" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R456" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="U456" t="inlineStr">
         <is>
@@ -66424,13 +66424,13 @@
         </is>
       </c>
       <c r="N458" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O458" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="R458" t="n">
-        <v>0.1415180660636405</v>
+        <v>0.283036132127281</v>
       </c>
       <c r="U458" t="inlineStr">
         <is>
@@ -66568,13 +66568,13 @@
         </is>
       </c>
       <c r="N459" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O459" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R459" t="n">
-        <v>0.07075903303182025</v>
+        <v>0.08844879128977531</v>
       </c>
       <c r="U459" t="inlineStr">
         <is>
@@ -66856,13 +66856,13 @@
         </is>
       </c>
       <c r="N461" t="n">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="O461" t="n">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="R461" t="n">
-        <v>1.309042111088675</v>
+        <v>2.600394463919394</v>
       </c>
       <c r="U461" t="inlineStr">
         <is>
@@ -67000,13 +67000,13 @@
         </is>
       </c>
       <c r="N462" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O462" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R462" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="U462" t="inlineStr">
         <is>
@@ -67144,13 +67144,13 @@
         </is>
       </c>
       <c r="N463" t="n">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="O463" t="n">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="R463" t="n">
-        <v>1.839734858827326</v>
+        <v>2.936499870820541</v>
       </c>
       <c r="U463" t="inlineStr">
         <is>
@@ -67543,7 +67543,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17355</v>
+        <v>17772</v>
       </c>
     </row>
     <row r="16">
